--- a/data/trans_camb/BARTHEL_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Estudios-trans_camb.xlsx
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-8,32</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,73</t>
+          <t>10,73</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-13,3</t>
+          <t>13,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-11,59</t>
+          <t>11,59</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,23</t>
+          <t>16,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-11,3</t>
+          <t>11,3</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,5</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,47</t>
+          <t>14,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; -3,47</t>
+          <t>3,18; 13,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -1,85</t>
+          <t>1,33; 11,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -5,64</t>
+          <t>6,38; 15,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -8,62</t>
+          <t>8,68; 18,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,8; -6,66</t>
+          <t>6,72; 16,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,26; -11,63</t>
+          <t>11,98; 20,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,72; -7,72</t>
+          <t>7,66; 14,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; -6,08</t>
+          <t>5,8; 12,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,82; -11,27</t>
+          <t>11,38; 17,86</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-9,21%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-6,92%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,87%</t>
+          <t>111,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-15,47%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-13,47%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-18,88%</t>
+          <t>115,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-12,89%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-10,84%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,5%</t>
+          <t>117,53%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,83; -3,93</t>
+          <t>27,2; 184,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,9; -1,95</t>
+          <t>12,18; 150,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -6,35</t>
+          <t>51,48; 210,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,89; -10,26</t>
+          <t>53,98; 151,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,07; -7,93</t>
+          <t>40,15; 137,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,12; -13,94</t>
+          <t>72,28; 172,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -8,96</t>
+          <t>53,59; 136,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -7,11</t>
+          <t>42,86; 119,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -13,12</t>
+          <t>81,43; 171,25</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-4,05</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,15</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-4,77</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-5,1</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-4,23</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 1,39</t>
+          <t>-1,57; 9,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,94</t>
+          <t>-1,56; 6,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -1,13</t>
+          <t>0,84; 9,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 3,74</t>
+          <t>-5,9; 17,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 5,11</t>
+          <t>-5,87; 12,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 17,49</t>
+          <t>-17,23; 5,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 0,64</t>
+          <t>0,06; 10,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 1,1</t>
+          <t>-0,67; 8,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 5,0</t>
+          <t>-4,47; 6,77</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-4,17%</t>
+          <t>145,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-2,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,33%</t>
+          <t>221,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-7,26%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-5,22%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>-21,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-5,38%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,46%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,51%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 1,4</t>
+          <t>-53,7; 1380,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,02</t>
+          <t>-47,74; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -1,21</t>
+          <t>6,5; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 4,28</t>
+          <t>-46,35; 416,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 5,52</t>
+          <t>-43,61; 356,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 22,54</t>
+          <t>-82,03; 105,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 0,71</t>
+          <t>-9,15; 404,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 1,14</t>
+          <t>-12,57; 313,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 5,67</t>
+          <t>-47,22; 216,5</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,03</t>
+          <t>4,03</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,42</t>
+          <t>-8,42</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>-5,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>-0,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 7,32</t>
+          <t>-7,35; 11,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 6,16</t>
+          <t>-5,03; 15,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 10,25</t>
+          <t>-10,87; 7,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,58; 18,88</t>
+          <t>-17,06; 24,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 25,01</t>
+          <t>-25,3; 5,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 24,81</t>
+          <t>-23,09; 5,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 8,14</t>
+          <t>-8,0; 13,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 10,84</t>
+          <t>-9,89; 7,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 10,26</t>
+          <t>-10,46; 4,66</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-4,18%</t>
+          <t>114,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,93%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,74%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>-67,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>-41,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-1,87%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>-14,97%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>-12,52%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 7,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 5,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 11,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 24,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 33,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 36,09</t>
+          <t>-85,56; 164,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 9,26</t>
+          <t>-80,35; 543,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 12,67</t>
+          <t>-88,11; 436,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 12,13</t>
+          <t>-72,29; 216,5</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-12,13</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-8,27</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-9,89</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>6,39</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>5,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -2,97</t>
+          <t>2,99; 10,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; -0,69</t>
+          <t>0,46; 7,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; -2,0</t>
+          <t>1,95; 8,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -7,78</t>
+          <t>7,78; 16,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -3,74</t>
+          <t>3,75; 12,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 5,17</t>
+          <t>-5,18; 10,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -6,93</t>
+          <t>6,77; 12,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -3,48</t>
+          <t>3,72; 9,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,35</t>
+          <t>-1,67; 8,37</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-7,59%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-4,31%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,6%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-14,02%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-9,56%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,5%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-11,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-7,19%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,76%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -3,35</t>
+          <t>30,18; 167,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,75</t>
+          <t>4,03; 113,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,93; -2,13</t>
+          <t>18,72; 128,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; -9,34</t>
+          <t>48,12; 145,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -4,5</t>
+          <t>23,88; 106,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 6,21</t>
+          <t>-32,73; 81,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,46; -7,96</t>
+          <t>54,03; 131,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,07; -4,01</t>
+          <t>29,69; 91,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 1,58</t>
+          <t>-8,43; 81,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/BARTHEL_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,73</t>
+          <t>10,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,23</t>
+          <t>16,45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,47</t>
+          <t>14,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,27</t>
+          <t>3,52; 13,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,04</t>
+          <t>1,09; 10,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,71</t>
+          <t>5,41; 14,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 18,09</t>
+          <t>8,09; 18,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 16,52</t>
+          <t>6,65; 16,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 20,22</t>
+          <t>12,62; 20,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 14,98</t>
+          <t>7,73; 14,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 12,96</t>
+          <t>6,17; 12,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 17,86</t>
+          <t>11,32; 17,74</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111,2%</t>
+          <t>106,12%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>115,95%</t>
+          <t>117,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117,53%</t>
+          <t>117,28%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,2; 184,08</t>
+          <t>27,81; 176,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,18; 150,67</t>
+          <t>8,06; 141,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,48; 210,04</t>
+          <t>43,01; 190,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,98; 151,72</t>
+          <t>47,57; 148,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,15; 137,32</t>
+          <t>39,52; 137,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,28; 172,52</t>
+          <t>77,65; 181,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,59; 136,35</t>
+          <t>55,01; 133,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>42,86; 119,5</t>
+          <t>43,28; 117,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,43; 171,25</t>
+          <t>79,01; 165,33</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>5,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 9,76</t>
+          <t>-1,29; 9,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,73</t>
+          <t>-2,24; 6,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,82</t>
+          <t>0,83; 9,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 17,12</t>
+          <t>-5,07; 17,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 12,75</t>
+          <t>-6,09; 12,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 5,76</t>
+          <t>-4,88; 10,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 10,92</t>
+          <t>-0,49; 11,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 8,67</t>
+          <t>-1,33; 8,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 6,77</t>
+          <t>1,0; 9,03</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221,39%</t>
+          <t>207,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-21,81%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>104,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,7; 1380,91</t>
+          <t>-52,64; 1136,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,74; —</t>
+          <t>-44,52; 792,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,5; —</t>
+          <t>3,36; 1051,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 416,19</t>
+          <t>-40,99; 467,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 356,86</t>
+          <t>-42,87; 415,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 105,86</t>
+          <t>-29,29; 312,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 404,57</t>
+          <t>-8,84; 423,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 313,11</t>
+          <t>-20,7; 351,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,22; 216,5</t>
+          <t>5,7; 357,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-5,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 11,86</t>
+          <t>-7,44; 11,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 15,3</t>
+          <t>-5,48; 16,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 7,01</t>
+          <t>-10,79; 7,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 24,43</t>
+          <t>-15,8; 24,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 5,63</t>
+          <t>-25,44; 4,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 5,51</t>
+          <t>-23,08; 5,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 13,61</t>
+          <t>-8,77; 13,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 7,75</t>
+          <t>-10,39; 7,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 4,66</t>
+          <t>-10,2; 4,81</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,15%</t>
+          <t>-45,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-12,52%</t>
+          <t>-13,88%</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,56; 164,84</t>
+          <t>-85,11; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,35; 543,43</t>
+          <t>-100,0; 476,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,11; 436,85</t>
+          <t>-90,9; 430,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,29; 216,5</t>
+          <t>-71,08; 263,36</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>9,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>7,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,37</t>
+          <t>3,09; 10,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 7,08</t>
+          <t>0,94; 7,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,08</t>
+          <t>1,67; 7,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 16,61</t>
+          <t>8,08; 16,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 12,38</t>
+          <t>4,09; 12,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 10,2</t>
+          <t>5,61; 12,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 12,85</t>
+          <t>6,96; 13,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,12</t>
+          <t>3,38; 9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 8,37</t>
+          <t>4,62; 9,66</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,18; 167,72</t>
+          <t>30,64; 168,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 113,9</t>
+          <t>8,32; 118,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,72; 128,8</t>
+          <t>16,6; 127,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48,12; 145,99</t>
+          <t>50,95; 143,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,88; 106,79</t>
+          <t>25,75; 112,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 81,27</t>
+          <t>34,85; 117,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,03; 131,41</t>
+          <t>54,76; 133,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,69; 91,25</t>
+          <t>28,28; 93,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 81,97</t>
+          <t>34,67; 98,86</t>
         </is>
       </c>
     </row>
